--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F04C38E-754C-4F2D-9D10-25AF72EB37F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58B47EC-B706-455C-8546-1B70D0F1243B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Weekend project work and self-study</t>
+  </si>
+  <si>
+    <t>prepareing netoworking ca</t>
   </si>
 </sst>
 </file>
@@ -1864,26 +1867,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46240</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>50</v>
+      </c>
+      <c r="D24" s="14">
+        <v>250</v>
+      </c>
+      <c r="E24" s="14">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>250</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58B47EC-B706-455C-8546-1B70D0F1243B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B03A5-9910-4B1D-9526-CA6403F050B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>prepareing netoworking ca</t>
+  </si>
+  <si>
+    <t>Revised networking concepts and spent time practicing coding.</t>
   </si>
 </sst>
 </file>
@@ -1912,27 +1915,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46241</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>260</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>200</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B03A5-9910-4B1D-9526-CA6403F050B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A67FDA7-8214-4F4D-9C2D-7D680A80F45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Revised networking concepts and spent time practicing coding.</t>
+  </si>
+  <si>
+    <t>Attended college and practiced coding in the evening</t>
   </si>
 </sst>
 </file>
@@ -1961,27 +1964,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46242</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>300</v>
+      </c>
+      <c r="E26" s="14">
+        <v>50</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>180</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A67FDA7-8214-4F4D-9C2D-7D680A80F45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008BA7D3-27C2-49CD-AB37-8A0E63BB3D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Attended college and practiced coding in the evening</t>
+  </si>
+  <si>
+    <t>Revised my notes and prepared for the next college week.</t>
   </si>
 </sst>
 </file>
@@ -2010,27 +2013,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>320</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>180</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008BA7D3-27C2-49CD-AB37-8A0E63BB3D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE953E7-F774-4A65-AE7D-161E6ECA3800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,18 @@
   </si>
   <si>
     <t>Revised my notes and prepared for the next college week.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>I felt tried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was practice analytical </t>
+  </si>
+  <si>
+    <t>I was practice for python ca</t>
   </si>
 </sst>
 </file>
@@ -2060,70 +2072,142 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B28" s="14">
+        <v>400</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>180</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>40</v>
+      </c>
+      <c r="D29" s="14">
+        <v>300</v>
+      </c>
+      <c r="E29" s="14">
+        <v>70</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>150</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>350</v>
+      </c>
+      <c r="E30" s="14">
+        <v>100</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE953E7-F774-4A65-AE7D-161E6ECA3800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BB7D99-5FA4-4D4B-8253-27EB34DAA849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2210,26 +2210,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B31" s="14">
+        <v>400</v>
+      </c>
+      <c r="C31" s="14">
+        <v>70</v>
+      </c>
+      <c r="D31" s="14">
+        <v>300</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>180</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45BB7D99-5FA4-4D4B-8253-27EB34DAA849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D7DB6C-2B60-47DC-AEE2-982C30978C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,15 @@
   </si>
   <si>
     <t>I was practice for python ca</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>I was not felling well</t>
+  </si>
+  <si>
+    <t>I was preparing ca for python</t>
   </si>
 </sst>
 </file>
@@ -2256,48 +2265,96 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B32" s="14">
+        <v>350</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>3</v>
+      </c>
+      <c r="G32" s="14">
+        <v>150</v>
+      </c>
+      <c r="H32" s="14">
+        <v>250</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>903</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>537</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B33" s="14">
+        <v>400</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>300</v>
+      </c>
+      <c r="E33" s="14">
+        <v>50</v>
+      </c>
+      <c r="F33" s="14">
+        <v>6</v>
+      </c>
+      <c r="G33" s="14">
+        <v>300</v>
+      </c>
+      <c r="H33" s="14">
+        <v>200</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>996</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>444</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D7DB6C-2B60-47DC-AEE2-982C30978C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B10F11-79A2-4521-97BE-980BE4BE15A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>I was preparing ca for python</t>
+  </si>
+  <si>
+    <t>I was preparing ca for analytical</t>
   </si>
 </sst>
 </file>
@@ -2357,48 +2360,96 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>250</v>
+      </c>
+      <c r="E34" s="14">
+        <v>40</v>
+      </c>
+      <c r="F34" s="14">
+        <v>6</v>
+      </c>
+      <c r="G34" s="14">
+        <v>300</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>956</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>484</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B35" s="14">
+        <v>450</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>300</v>
+      </c>
+      <c r="E35" s="14">
+        <v>50</v>
+      </c>
+      <c r="F35" s="14">
+        <v>6</v>
+      </c>
+      <c r="G35" s="14">
+        <v>300</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1046</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>394</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B10F11-79A2-4521-97BE-980BE4BE15A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43022C02-C136-4DE9-97EA-203B208DBBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>I was preparing ca for analytical</t>
+  </si>
+  <si>
+    <t>I started minor project</t>
   </si>
 </sst>
 </file>
@@ -2284,21 +2287,21 @@
         <v>60</v>
       </c>
       <c r="F32" s="14">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14">
         <v>3</v>
-      </c>
-      <c r="G32" s="14">
-        <v>150</v>
       </c>
       <c r="H32" s="14">
         <v>250</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>903</v>
+        <v>1050</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>537</v>
+        <v>390</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>78</v>
@@ -2330,21 +2333,21 @@
         <v>50</v>
       </c>
       <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
         <v>6</v>
-      </c>
-      <c r="G33" s="14">
-        <v>300</v>
       </c>
       <c r="H33" s="14">
         <v>200</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>996</v>
+        <v>1290</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>444</v>
+        <v>150</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>55</v>
@@ -2376,21 +2379,21 @@
         <v>40</v>
       </c>
       <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
         <v>6</v>
-      </c>
-      <c r="G34" s="14">
-        <v>300</v>
       </c>
       <c r="H34" s="14">
         <v>180</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>956</v>
+        <v>1250</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>484</v>
+        <v>190</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>55</v>
@@ -2422,21 +2425,21 @@
         <v>50</v>
       </c>
       <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
         <v>6</v>
-      </c>
-      <c r="G35" s="14">
-        <v>300</v>
       </c>
       <c r="H35" s="14">
         <v>180</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1046</v>
+        <v>1340</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>394</v>
+        <v>100</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>55</v>
@@ -2452,48 +2455,96 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B36" s="14">
+        <v>450</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>50</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>180</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B37" s="14">
+        <v>380</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>300</v>
+      </c>
+      <c r="E37" s="14">
+        <v>40</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>150</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43022C02-C136-4DE9-97EA-203B208DBBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DCDEBB-0909-4E74-904C-21F97AD54F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>I started minor project</t>
+  </si>
+  <si>
+    <t>working on project</t>
   </si>
 </sst>
 </file>
@@ -2547,26 +2550,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B38" s="14">
+        <v>400</v>
+      </c>
+      <c r="C38" s="14">
+        <v>40</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>40</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>300</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DCDEBB-0909-4E74-904C-21F97AD54F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EF0315-6086-469F-8E75-D819D5B07A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -300,7 +300,13 @@
     <t>I started minor project</t>
   </si>
   <si>
-    <t>working on project</t>
+    <t>I was working on project</t>
+  </si>
+  <si>
+    <t>I was doing coding in cpp</t>
+  </si>
+  <si>
+    <t>weather is good</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46253</v>
       </c>
@@ -2596,48 +2602,96 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B39" s="14">
+        <v>400</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>300</v>
+      </c>
+      <c r="E39" s="14">
+        <v>40</v>
+      </c>
+      <c r="F39" s="14">
+        <v>150</v>
+      </c>
+      <c r="G39" s="14">
+        <v>3</v>
+      </c>
+      <c r="H39" s="14">
+        <v>180</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>50</v>
+      </c>
+      <c r="D40" s="14">
+        <v>350</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>200</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EF0315-6086-469F-8E75-D819D5B07A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E036B44A-09DD-4E53-BADA-A5148782A503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -489,6 +489,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1729,7 +1732,7 @@
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46236</v>
+        <v>46267</v>
       </c>
       <c r="B20" s="14">
         <v>420</v>
@@ -1775,7 +1778,7 @@
     </row>
     <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46237</v>
+        <v>46268</v>
       </c>
       <c r="B21" s="14">
         <v>400</v>
@@ -1821,7 +1824,7 @@
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46238</v>
+        <v>46269</v>
       </c>
       <c r="B22" s="14">
         <v>420</v>
@@ -1867,7 +1870,7 @@
     </row>
     <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="B23" s="14">
         <v>480</v>
@@ -1913,7 +1916,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46240</v>
+        <v>46271</v>
       </c>
       <c r="B24" s="14">
         <v>420</v>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="B25" s="14">
         <v>480</v>
@@ -2005,7 +2008,7 @@
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46242</v>
+        <v>46273</v>
       </c>
       <c r="B26" s="14">
         <v>400</v>
@@ -2051,7 +2054,7 @@
     </row>
     <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46243</v>
+        <v>46274</v>
       </c>
       <c r="B27" s="14">
         <v>420</v>
@@ -2096,8 +2099,8 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>46244</v>
+      <c r="A28" s="21">
+        <v>46275</v>
       </c>
       <c r="B28" s="14">
         <v>400</v>
@@ -2142,8 +2145,8 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
-        <v>46245</v>
+      <c r="A29" s="21">
+        <v>46276</v>
       </c>
       <c r="B29" s="14">
         <v>420</v>
@@ -2188,8 +2191,8 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
-        <v>46246</v>
+      <c r="A30" s="21">
+        <v>46277</v>
       </c>
       <c r="B30" s="14">
         <v>480</v>
@@ -2234,8 +2237,8 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
-        <v>46247</v>
+      <c r="A31" s="21">
+        <v>46278</v>
       </c>
       <c r="B31" s="14">
         <v>400</v>
@@ -2280,8 +2283,8 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
-        <v>46248</v>
+      <c r="A32" s="21">
+        <v>46279</v>
       </c>
       <c r="B32" s="14">
         <v>350</v>
@@ -2326,8 +2329,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
-        <v>46249</v>
+      <c r="A33" s="21">
+        <v>46280</v>
       </c>
       <c r="B33" s="14">
         <v>400</v>
@@ -2372,8 +2375,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
-        <v>46250</v>
+      <c r="A34" s="21">
+        <v>46281</v>
       </c>
       <c r="B34" s="14">
         <v>420</v>
@@ -2418,8 +2421,8 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13">
-        <v>46251</v>
+      <c r="A35" s="21">
+        <v>46282</v>
       </c>
       <c r="B35" s="14">
         <v>450</v>
@@ -2464,8 +2467,8 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13">
-        <v>46252</v>
+      <c r="A36" s="21">
+        <v>46283</v>
       </c>
       <c r="B36" s="14">
         <v>450</v>
@@ -2510,8 +2513,8 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13">
-        <v>46253</v>
+      <c r="A37" s="21">
+        <v>46284</v>
       </c>
       <c r="B37" s="14">
         <v>380</v>
@@ -2556,8 +2559,8 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13">
-        <v>46254</v>
+      <c r="A38" s="21">
+        <v>46285</v>
       </c>
       <c r="B38" s="14">
         <v>400</v>
@@ -2602,8 +2605,8 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13">
-        <v>46255</v>
+      <c r="A39" s="21">
+        <v>46286</v>
       </c>
       <c r="B39" s="14">
         <v>400</v>
@@ -2648,8 +2651,8 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13">
-        <v>46256</v>
+      <c r="A40" s="21">
+        <v>46287</v>
       </c>
       <c r="B40" s="14">
         <v>420</v>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E036B44A-09DD-4E53-BADA-A5148782A503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D3C04A-D6F1-49B8-A68C-1B0A349FBB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,12 @@
   <si>
     <t>weather is good</t>
   </si>
+  <si>
+    <t>worked on python practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was learning new language </t>
+  </si>
 </sst>
 </file>
 
@@ -445,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -489,9 +495,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,7 +963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N403"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1088,7 +1091,7 @@
     </row>
     <row r="6" spans="1:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="9">
         <v>480</v>
@@ -1112,11 +1115,11 @@
         <v>60</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I71" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1110</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J71" si="1">IF(I6="","",1440-I6)</f>
         <v>330</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1132,1053 +1135,1049 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+    <row r="7" spans="1:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="9">
+        <v>420</v>
+      </c>
+      <c r="C7" s="9">
+        <v>40</v>
+      </c>
+      <c r="D7" s="9">
+        <v>250</v>
+      </c>
+      <c r="E7" s="9">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9">
+        <v>300</v>
+      </c>
+      <c r="G7" s="9">
+        <v>6</v>
+      </c>
+      <c r="H7" s="9">
+        <v>180</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1240</v>
+      </c>
+      <c r="J7" s="10">
+        <v>200</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="9">
+        <v>400</v>
+      </c>
+      <c r="C8" s="9">
+        <v>50</v>
+      </c>
+      <c r="D8" s="9">
+        <v>300</v>
+      </c>
+      <c r="E8" s="9">
+        <v>50</v>
+      </c>
+      <c r="F8" s="9">
+        <v>300</v>
+      </c>
+      <c r="G8" s="9">
+        <v>6</v>
+      </c>
+      <c r="H8" s="9">
+        <v>170</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1270</v>
+      </c>
+      <c r="J8" s="10">
+        <v>170</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>46254</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B9" s="14">
         <v>420</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C9" s="14">
         <v>45</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D9" s="14">
         <v>200</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E9" s="14">
         <v>75</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F9" s="14">
         <v>300</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G9" s="14">
         <v>6</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H9" s="14">
         <v>80</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N9" s="17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>46255</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B10" s="14">
         <v>480</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C10" s="14">
         <v>60</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D10" s="14">
         <v>220</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E10" s="14">
         <v>65</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F10" s="14">
         <v>300</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G10" s="14">
         <v>6</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H10" s="14">
         <v>90</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
         <v>1215</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N10" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
         <v>46256</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B11" s="14">
         <v>480</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C11" s="14">
         <v>50</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D11" s="14">
         <v>300</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E11" s="14">
         <v>75</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F11" s="14">
         <v>0</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H11" s="14">
         <v>120</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
         <v>1025</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>415</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N11" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
         <v>46257</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B12" s="14">
         <v>480</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C12" s="14">
         <v>60</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D12" s="14">
         <v>300</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E12" s="14">
         <v>60</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F12" s="14">
         <v>0</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G12" s="14">
         <v>0</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H12" s="14">
         <v>150</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N12" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>46258</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B13" s="14">
         <v>480</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C13" s="14">
         <v>50</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D13" s="14">
         <v>250</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E13" s="14">
         <v>40</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F13" s="14">
         <v>150</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G13" s="14">
         <v>3</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H13" s="14">
         <v>150</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N13" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
         <v>46259</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B14" s="14">
         <v>420</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C14" s="14">
         <v>40</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D14" s="14">
         <v>180</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E14" s="14">
         <v>60</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F14" s="14">
         <v>300</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G14" s="14">
         <v>6</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H14" s="14">
         <v>180</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
         <v>1180</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N14" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>46260</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B15" s="14">
         <v>480</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C15" s="14">
         <v>60</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D15" s="14">
         <v>240</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E15" s="14">
         <v>60</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F15" s="14">
         <v>300</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G15" s="14">
         <v>6</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H15" s="14">
         <v>200</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
         <v>1340</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N15" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>46261</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B16" s="14">
         <v>420</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C16" s="14">
         <v>50</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D16" s="14">
         <v>200</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E16" s="14">
         <v>50</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F16" s="14">
         <v>300</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G16" s="14">
         <v>5</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H16" s="14">
         <v>150</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
         <v>1170</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N16" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
         <v>46262</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B17" s="14">
         <v>480</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C17" s="14">
         <v>60</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D17" s="14">
         <v>108</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E17" s="14">
         <v>50</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F17" s="14">
         <v>300</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G17" s="14">
         <v>4</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H17" s="14">
         <v>180</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
         <v>1178</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>262</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="L17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N17" s="17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
         <v>46263</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B18" s="14">
         <v>420</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C18" s="14">
         <v>50</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D18" s="14">
         <v>150</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E18" s="14">
         <v>50</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F18" s="14">
         <v>0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G18" s="14">
         <v>0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H18" s="14">
         <v>220</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K18" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L18" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M18" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N18" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
         <v>46264</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B19" s="14">
         <v>480</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C19" s="14">
         <v>60</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D19" s="14">
         <v>180</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E19" s="14">
         <v>60</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F19" s="14">
         <v>0</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G19" s="14">
         <v>0</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H19" s="14">
         <v>180</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="L19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N19" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
         <v>46265</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B20" s="14">
         <v>420</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C20" s="14">
         <v>40</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D20" s="14">
         <v>150</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E20" s="14">
         <v>50</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F20" s="14">
         <v>150</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G20" s="14">
         <v>3</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H20" s="14">
         <v>150</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M20" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N20" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
         <v>46266</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B21" s="14">
         <v>480</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C21" s="14">
         <v>60</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D21" s="14">
         <v>180</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E21" s="14">
         <v>40</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F21" s="14">
         <v>300</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G21" s="14">
         <v>6</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H21" s="14">
         <v>180</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
         <v>1240</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K21" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="17" t="s">
+      <c r="N21" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
         <v>46267</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B22" s="14">
         <v>420</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C22" s="14">
         <v>40</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D22" s="14">
         <v>180</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E22" s="14">
         <v>40</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F22" s="14">
         <v>300</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G22" s="14">
         <v>6</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H22" s="14">
         <v>200</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
         <v>1180</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K22" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="L22" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M22" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N22" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
         <v>46268</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B23" s="14">
         <v>400</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C23" s="14">
         <v>60</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D23" s="14">
         <v>240</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E23" s="14">
         <v>50</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F23" s="14">
         <v>300</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G23" s="14">
         <v>6</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H23" s="14">
         <v>180</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
         <v>1230</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K23" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L23" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M21" s="16" t="s">
+      <c r="M23" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N23" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
         <v>46269</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B24" s="14">
         <v>420</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C24" s="14">
         <v>50</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D24" s="14">
         <v>180</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E24" s="14">
         <v>60</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F24" s="14">
         <v>300</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G24" s="14">
         <v>6</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H24" s="14">
         <v>180</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
         <v>1190</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K24" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="16" t="s">
+      <c r="L24" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N24" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
         <v>46270</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B25" s="14">
         <v>480</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C25" s="14">
         <v>60</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D25" s="14">
         <v>250</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E25" s="14">
         <v>50</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F25" s="14">
         <v>0</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G25" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H25" s="14">
         <v>180</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K25" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L23" s="16" t="s">
+      <c r="L25" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N25" s="17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
         <v>46271</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B26" s="14">
         <v>420</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C26" s="14">
         <v>50</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D26" s="14">
         <v>250</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E26" s="14">
         <v>40</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F26" s="14">
         <v>0</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G26" s="14">
         <v>0</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H26" s="14">
         <v>250</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K26" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L24" s="16" t="s">
+      <c r="L26" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M24" s="16" t="s">
+      <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N24" s="17" t="s">
+      <c r="N26" s="17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="13">
+    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
         <v>46272</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B27" s="14">
         <v>480</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C27" s="14">
         <v>60</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D27" s="14">
         <v>260</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E27" s="14">
         <v>60</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F27" s="14">
         <v>200</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H27" s="14">
         <v>180</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
         <v>1240</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K27" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L25" s="16" t="s">
+      <c r="L27" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="M27" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N25" s="17" t="s">
+      <c r="N27" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
         <v>46273</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B28" s="14">
         <v>400</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C28" s="14">
         <v>30</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D28" s="14">
         <v>300</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E28" s="14">
         <v>50</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F28" s="14">
         <v>300</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G28" s="14">
         <v>6</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H28" s="14">
         <v>180</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
         <v>1260</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K28" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L26" s="16" t="s">
+      <c r="L28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M28" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="17" t="s">
+      <c r="N28" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
         <v>46274</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B29" s="14">
         <v>420</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C29" s="14">
         <v>40</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D29" s="14">
         <v>320</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E29" s="14">
         <v>60</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F29" s="14">
         <v>300</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G29" s="14">
         <v>6</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H29" s="14">
         <v>180</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K29" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="21">
-        <v>46275</v>
-      </c>
-      <c r="B28" s="14">
-        <v>400</v>
-      </c>
-      <c r="C28" s="14">
-        <v>60</v>
-      </c>
-      <c r="D28" s="14">
-        <v>180</v>
-      </c>
-      <c r="E28" s="14">
-        <v>50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>300</v>
-      </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
-      <c r="H28" s="14">
-        <v>180</v>
-      </c>
-      <c r="I28" s="15">
-        <f t="shared" si="0"/>
-        <v>1170</v>
-      </c>
-      <c r="J28" s="15">
-        <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="21">
-        <v>46276</v>
-      </c>
-      <c r="B29" s="14">
-        <v>420</v>
-      </c>
-      <c r="C29" s="14">
-        <v>40</v>
-      </c>
-      <c r="D29" s="14">
-        <v>300</v>
-      </c>
-      <c r="E29" s="14">
-        <v>70</v>
-      </c>
-      <c r="F29" s="14">
-        <v>300</v>
-      </c>
-      <c r="G29" s="14">
-        <v>6</v>
-      </c>
-      <c r="H29" s="14">
-        <v>150</v>
-      </c>
-      <c r="I29" s="15">
-        <f t="shared" si="0"/>
-        <v>1280</v>
-      </c>
-      <c r="J29" s="15">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>50</v>
@@ -2187,30 +2186,30 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="21">
-        <v>46277</v>
+      <c r="A30" s="13">
+        <v>46275</v>
       </c>
       <c r="B30" s="14">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="C30" s="14">
         <v>60</v>
       </c>
       <c r="D30" s="14">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="E30" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F30" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G30" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H30" s="14">
         <v>180</v>
@@ -2224,142 +2223,142 @@
         <v>270</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="21">
-        <v>46278</v>
+      <c r="A31" s="13">
+        <v>46276</v>
       </c>
       <c r="B31" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C31" s="14">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D31" s="14">
         <v>300</v>
       </c>
       <c r="E31" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F31" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G31" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" s="14">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1280</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>160</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="21">
-        <v>46279</v>
+      <c r="A32" s="13">
+        <v>46277</v>
       </c>
       <c r="B32" s="14">
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="C32" s="14">
         <v>60</v>
       </c>
       <c r="D32" s="14">
+        <v>350</v>
+      </c>
+      <c r="E32" s="14">
+        <v>100</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
         <v>180</v>
-      </c>
-      <c r="E32" s="14">
-        <v>60</v>
-      </c>
-      <c r="F32" s="14">
-        <v>150</v>
-      </c>
-      <c r="G32" s="14">
-        <v>3</v>
-      </c>
-      <c r="H32" s="14">
-        <v>250</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1170</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="21">
-        <v>46280</v>
+      <c r="A33" s="13">
+        <v>46278</v>
       </c>
       <c r="B33" s="14">
         <v>400</v>
       </c>
       <c r="C33" s="14">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D33" s="14">
         <v>300</v>
       </c>
       <c r="E33" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F33" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1010</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>430</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>55</v>
@@ -2371,64 +2370,64 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="21">
-        <v>46281</v>
+      <c r="A34" s="13">
+        <v>46279</v>
       </c>
       <c r="B34" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="C34" s="14">
         <v>60</v>
       </c>
       <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>150</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
         <v>250</v>
-      </c>
-      <c r="E34" s="14">
-        <v>40</v>
-      </c>
-      <c r="F34" s="14">
-        <v>300</v>
-      </c>
-      <c r="G34" s="14">
-        <v>6</v>
-      </c>
-      <c r="H34" s="14">
-        <v>180</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="21">
-        <v>46282</v>
+      <c r="A35" s="13">
+        <v>46280</v>
       </c>
       <c r="B35" s="14">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C35" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D35" s="14">
         <v>300</v>
@@ -2443,44 +2442,44 @@
         <v>6</v>
       </c>
       <c r="H35" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1340</v>
+        <v>1290</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="21">
-        <v>46283</v>
+      <c r="A36" s="13">
+        <v>46281</v>
       </c>
       <c r="B36" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>250</v>
+      </c>
+      <c r="E36" s="14">
         <v>40</v>
-      </c>
-      <c r="D36" s="14">
-        <v>180</v>
-      </c>
-      <c r="E36" s="14">
-        <v>50</v>
       </c>
       <c r="F36" s="14">
         <v>300</v>
@@ -2493,14 +2492,14 @@
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>55</v>
@@ -2509,15 +2508,15 @@
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="21">
-        <v>46284</v>
+      <c r="A37" s="13">
+        <v>46282</v>
       </c>
       <c r="B37" s="14">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="C37" s="14">
         <v>60</v>
@@ -2526,24 +2525,24 @@
         <v>300</v>
       </c>
       <c r="E37" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F37" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G37" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37" s="14">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>1340</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>100</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>55</v>
@@ -2555,15 +2554,15 @@
         <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
-        <v>46285</v>
+      <c r="A38" s="13">
+        <v>46283</v>
       </c>
       <c r="B38" s="14">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C38" s="14">
         <v>40</v>
@@ -2572,44 +2571,44 @@
         <v>180</v>
       </c>
       <c r="E38" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F38" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G38" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H38" s="14">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1200</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="21">
-        <v>46286</v>
+      <c r="A39" s="13">
+        <v>46284</v>
       </c>
       <c r="B39" s="14">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C39" s="14">
         <v>60</v>
@@ -2621,168 +2620,264 @@
         <v>40</v>
       </c>
       <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
         <v>150</v>
-      </c>
-      <c r="G39" s="14">
-        <v>3</v>
-      </c>
-      <c r="H39" s="14">
-        <v>180</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>930</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>510</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="21">
-        <v>46287</v>
+      <c r="A40" s="13">
+        <v>46285</v>
       </c>
       <c r="B40" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C40" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D40" s="14">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="E40" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
         <v>300</v>
-      </c>
-      <c r="G40" s="14">
-        <v>6</v>
-      </c>
-      <c r="H40" s="14">
-        <v>200</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1380</v>
+        <v>960</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>400</v>
+      </c>
+      <c r="C41" s="14">
         <v>60</v>
       </c>
-      <c r="K40" s="16" t="s">
+      <c r="D41" s="14">
+        <v>300</v>
+      </c>
+      <c r="E41" s="14">
+        <v>40</v>
+      </c>
+      <c r="F41" s="14">
+        <v>150</v>
+      </c>
+      <c r="G41" s="14">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14">
+        <v>180</v>
+      </c>
+      <c r="I41" s="15">
+        <f t="shared" si="0"/>
+        <v>1130</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" si="1"/>
+        <v>310</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>50</v>
+      </c>
+      <c r="D42" s="14">
+        <v>350</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>300</v>
+      </c>
+      <c r="G42" s="14">
+        <v>6</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="0"/>
+        <v>1380</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="K42" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L40" s="16" t="s">
+      <c r="L42" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M40" s="16" t="s">
+      <c r="M42" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="N40" s="17" t="s">
+      <c r="N42" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>50</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>50</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>430</v>
+      </c>
+      <c r="C44" s="14">
+        <v>60</v>
+      </c>
+      <c r="D44" s="14">
+        <v>250</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>300</v>
+      </c>
+      <c r="G44" s="14">
+        <v>6</v>
+      </c>
+      <c r="H44" s="14">
+        <v>220</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
@@ -3344,11 +3439,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3366,11 +3461,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3388,11 +3483,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I72:I135" si="2">IF(SUM(B72:F72,H72)=0,"",SUM(B72:F72,H72))</f>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J72:J135" si="3">IF(I72="","",1440-I72)</f>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -4752,11 +4847,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4774,11 +4869,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4796,11 +4891,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I136:I199" si="4">IF(SUM(B136:F136,H136)=0,"",SUM(B136:F136,H136))</f>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J136:J199" si="5">IF(I136="","",1440-I136)</f>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -6160,11 +6255,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6182,11 +6277,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6204,11 +6299,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I200:I263" si="6">IF(SUM(B200:F200,H200)=0,"",SUM(B200:F200,H200))</f>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J200:J263" si="7">IF(I200="","",1440-I200)</f>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -7568,11 +7663,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7590,11 +7685,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7612,11 +7707,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I264:I327" si="8">IF(SUM(B264:F264,H264)=0,"",SUM(B264:F264,H264))</f>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J264:J327" si="9">IF(I264="","",1440-I264)</f>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8976,11 +9071,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8998,11 +9093,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9020,11 +9115,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I328:I391" si="10">IF(SUM(B328:F328,H328)=0,"",SUM(B328:F328,H328))</f>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J328:J391" si="11">IF(I328="","",1440-I328)</f>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -10384,11 +10479,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10406,11 +10501,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10428,11 +10523,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I392:I403" si="12">IF(SUM(B392:F392,H392)=0,"",SUM(B392:F392,H392))</f>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J392:J403" si="13">IF(I392="","",1440-I392)</f>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10638,6 +10733,50 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10647,21 +10786,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J403">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K403" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L403" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M403" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
